--- a/data/trans_orig/IMC_inf_R-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IMC_inf_R-Clase-trans_orig.xlsx
@@ -726,7 +726,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Obesidad intensa</t>
+          <t>Obsesidad intesa</t>
         </is>
       </c>
       <c r="C4" s="5" t="n">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Obesidad intensa</t>
+          <t>Obsesidad intesa</t>
         </is>
       </c>
       <c r="C10" s="5" t="n">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Obesidad intensa</t>
+          <t>Obsesidad intesa</t>
         </is>
       </c>
       <c r="C16" s="5" t="n">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Obesidad intensa</t>
+          <t>Obsesidad intesa</t>
         </is>
       </c>
       <c r="C22" s="5" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Obesidad intensa</t>
+          <t>Obsesidad intesa</t>
         </is>
       </c>
       <c r="C28" s="5" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>Obesidad intensa</t>
+          <t>Obsesidad intesa</t>
         </is>
       </c>
       <c r="C34" s="5" t="n">
@@ -3093,25 +3093,25 @@
         </is>
       </c>
       <c r="C37" s="5" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D37" s="5" t="n">
-        <v>21568</v>
+        <v>22218</v>
       </c>
       <c r="E37" s="5" t="n">
-        <v>15726</v>
+        <v>16352</v>
       </c>
       <c r="F37" s="5" t="n">
-        <v>27556</v>
+        <v>28154</v>
       </c>
       <c r="G37" s="6" t="n">
-        <v>0.3746291972914667</v>
+        <v>0.3859207210438606</v>
       </c>
       <c r="H37" s="6" t="n">
-        <v>0.2731580352745707</v>
+        <v>0.2840188063253029</v>
       </c>
       <c r="I37" s="6" t="n">
-        <v>0.4786305395697445</v>
+        <v>0.4890155760055525</v>
       </c>
       <c r="J37" s="5" t="n">
         <v>70</v>
@@ -3135,25 +3135,25 @@
         <v>0.7910209610854907</v>
       </c>
       <c r="Q37" s="5" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="R37" s="5" t="n">
-        <v>69670</v>
+        <v>70320</v>
       </c>
       <c r="S37" s="5" t="n">
-        <v>60780</v>
+        <v>61326</v>
       </c>
       <c r="T37" s="5" t="n">
-        <v>78280</v>
+        <v>78817</v>
       </c>
       <c r="U37" s="6" t="n">
-        <v>0.5571034452977214</v>
+        <v>0.5623016735719552</v>
       </c>
       <c r="V37" s="6" t="n">
-        <v>0.4860163905839842</v>
+        <v>0.4903814886592948</v>
       </c>
       <c r="W37" s="6" t="n">
-        <v>0.6259479746348877</v>
+        <v>0.630245273223827</v>
       </c>
     </row>
     <row r="38">
@@ -3164,25 +3164,25 @@
         </is>
       </c>
       <c r="C38" s="5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D38" s="5" t="n">
-        <v>3922</v>
+        <v>3272</v>
       </c>
       <c r="E38" s="5" t="n">
-        <v>1341</v>
+        <v>1288</v>
       </c>
       <c r="F38" s="5" t="n">
-        <v>7867</v>
+        <v>7085</v>
       </c>
       <c r="G38" s="6" t="n">
-        <v>0.06811995582434767</v>
+        <v>0.05682843207195376</v>
       </c>
       <c r="H38" s="6" t="n">
-        <v>0.02329478313458523</v>
+        <v>0.02237612049450198</v>
       </c>
       <c r="I38" s="6" t="n">
-        <v>0.1366506368218262</v>
+        <v>0.1230676457973898</v>
       </c>
       <c r="J38" s="5" t="n">
         <v>2</v>
@@ -3206,25 +3206,25 @@
         <v>0.05649409626663165</v>
       </c>
       <c r="Q38" s="5" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="R38" s="5" t="n">
-        <v>5175</v>
+        <v>4525</v>
       </c>
       <c r="S38" s="5" t="n">
-        <v>2549</v>
+        <v>1960</v>
       </c>
       <c r="T38" s="5" t="n">
-        <v>10256</v>
+        <v>9198</v>
       </c>
       <c r="U38" s="6" t="n">
-        <v>0.0413829654672796</v>
+        <v>0.03618473719304581</v>
       </c>
       <c r="V38" s="6" t="n">
-        <v>0.02038590446126599</v>
+        <v>0.01567039980323963</v>
       </c>
       <c r="W38" s="6" t="n">
-        <v>0.08201319297098494</v>
+        <v>0.0735522160805248</v>
       </c>
     </row>
     <row r="39">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>Obesidad intensa</t>
+          <t>Obsesidad intesa</t>
         </is>
       </c>
       <c r="C40" s="5" t="n">
@@ -3523,25 +3523,25 @@
         </is>
       </c>
       <c r="C43" s="5" t="n">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="D43" s="5" t="n">
-        <v>288608</v>
+        <v>289258</v>
       </c>
       <c r="E43" s="5" t="n">
-        <v>269673</v>
+        <v>270350</v>
       </c>
       <c r="F43" s="5" t="n">
-        <v>308299</v>
+        <v>309239</v>
       </c>
       <c r="G43" s="6" t="n">
-        <v>0.5014291313699674</v>
+        <v>0.5025585874380708</v>
       </c>
       <c r="H43" s="6" t="n">
-        <v>0.4685328200174333</v>
+        <v>0.469708694037614</v>
       </c>
       <c r="I43" s="6" t="n">
-        <v>0.5356413918183183</v>
+        <v>0.5372749968849155</v>
       </c>
       <c r="J43" s="5" t="n">
         <v>487</v>
@@ -3565,25 +3565,25 @@
         <v>0.6490039662805456</v>
       </c>
       <c r="Q43" s="5" t="n">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="R43" s="5" t="n">
-        <v>618787</v>
+        <v>619437</v>
       </c>
       <c r="S43" s="5" t="n">
-        <v>592516</v>
+        <v>592662</v>
       </c>
       <c r="T43" s="5" t="n">
-        <v>643713</v>
+        <v>644108</v>
       </c>
       <c r="U43" s="6" t="n">
-        <v>0.5537460241754526</v>
+        <v>0.5543277750665409</v>
       </c>
       <c r="V43" s="6" t="n">
-        <v>0.5302361239096098</v>
+        <v>0.5303676006442305</v>
       </c>
       <c r="W43" s="6" t="n">
-        <v>0.5760522900141399</v>
+        <v>0.5764058545410677</v>
       </c>
     </row>
     <row r="44">
@@ -3594,25 +3594,25 @@
         </is>
       </c>
       <c r="C44" s="5" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D44" s="5" t="n">
-        <v>25630</v>
+        <v>24980</v>
       </c>
       <c r="E44" s="5" t="n">
-        <v>18881</v>
+        <v>18642</v>
       </c>
       <c r="F44" s="5" t="n">
-        <v>34840</v>
+        <v>34219</v>
       </c>
       <c r="G44" s="6" t="n">
-        <v>0.04452999950024893</v>
+        <v>0.04340054343214553</v>
       </c>
       <c r="H44" s="6" t="n">
-        <v>0.03280485207063754</v>
+        <v>0.03238904061358113</v>
       </c>
       <c r="I44" s="6" t="n">
-        <v>0.06053191071190098</v>
+        <v>0.05945214429213793</v>
       </c>
       <c r="J44" s="5" t="n">
         <v>28</v>
@@ -3636,25 +3636,25 @@
         <v>0.04851986897922602</v>
       </c>
       <c r="Q44" s="5" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="R44" s="5" t="n">
-        <v>43952</v>
+        <v>43302</v>
       </c>
       <c r="S44" s="5" t="n">
-        <v>34653</v>
+        <v>34055</v>
       </c>
       <c r="T44" s="5" t="n">
-        <v>56086</v>
+        <v>55349</v>
       </c>
       <c r="U44" s="6" t="n">
-        <v>0.03933208297955525</v>
+        <v>0.03875033208846691</v>
       </c>
       <c r="V44" s="6" t="n">
-        <v>0.03101063925552328</v>
+        <v>0.03047569514710221</v>
       </c>
       <c r="W44" s="6" t="n">
-        <v>0.05019080179215774</v>
+        <v>0.04953157222432859</v>
       </c>
     </row>
     <row r="45">
@@ -3970,7 +3970,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Obesidad intensa</t>
+          <t>Obsesidad intesa</t>
         </is>
       </c>
       <c r="C4" s="5" t="n">
@@ -4400,7 +4400,7 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Obesidad intensa</t>
+          <t>Obsesidad intesa</t>
         </is>
       </c>
       <c r="C10" s="5" t="n">
@@ -4830,7 +4830,7 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Obesidad intensa</t>
+          <t>Obsesidad intesa</t>
         </is>
       </c>
       <c r="C16" s="5" t="n">
@@ -5260,7 +5260,7 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Obesidad intensa</t>
+          <t>Obsesidad intesa</t>
         </is>
       </c>
       <c r="C22" s="5" t="n">
@@ -5690,7 +5690,7 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Obesidad intensa</t>
+          <t>Obsesidad intesa</t>
         </is>
       </c>
       <c r="C28" s="5" t="n">
@@ -6120,7 +6120,7 @@
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>Obesidad intensa</t>
+          <t>Obsesidad intesa</t>
         </is>
       </c>
       <c r="C34" s="5" t="n">
@@ -6550,7 +6550,7 @@
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>Obesidad intensa</t>
+          <t>Obsesidad intesa</t>
         </is>
       </c>
       <c r="C40" s="5" t="n">
@@ -7214,7 +7214,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Obesidad intensa</t>
+          <t>Obsesidad intesa</t>
         </is>
       </c>
       <c r="C4" s="5" t="n">
@@ -7644,7 +7644,7 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Obesidad intensa</t>
+          <t>Obsesidad intesa</t>
         </is>
       </c>
       <c r="C10" s="5" t="n">
@@ -8074,7 +8074,7 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Obesidad intensa</t>
+          <t>Obsesidad intesa</t>
         </is>
       </c>
       <c r="C16" s="5" t="n">
@@ -8504,7 +8504,7 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Obesidad intensa</t>
+          <t>Obsesidad intesa</t>
         </is>
       </c>
       <c r="C22" s="5" t="n">
@@ -8934,7 +8934,7 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Obesidad intensa</t>
+          <t>Obsesidad intesa</t>
         </is>
       </c>
       <c r="C28" s="5" t="n">
@@ -9364,7 +9364,7 @@
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>Obesidad intensa</t>
+          <t>Obsesidad intesa</t>
         </is>
       </c>
       <c r="C34" s="5" t="n">
@@ -9794,7 +9794,7 @@
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>Obesidad intensa</t>
+          <t>Obsesidad intesa</t>
         </is>
       </c>
       <c r="C40" s="5" t="n">
@@ -10458,7 +10458,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Obesidad intensa</t>
+          <t>Obsesidad intesa</t>
         </is>
       </c>
       <c r="C4" s="5" t="n">
@@ -10888,7 +10888,7 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Obesidad intensa</t>
+          <t>Obsesidad intesa</t>
         </is>
       </c>
       <c r="C10" s="5" t="n">
@@ -11318,7 +11318,7 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Obesidad intensa</t>
+          <t>Obsesidad intesa</t>
         </is>
       </c>
       <c r="C16" s="5" t="n">
@@ -11748,7 +11748,7 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Obesidad intensa</t>
+          <t>Obsesidad intesa</t>
         </is>
       </c>
       <c r="C22" s="5" t="n">
@@ -12178,7 +12178,7 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Obesidad intensa</t>
+          <t>Obsesidad intesa</t>
         </is>
       </c>
       <c r="C28" s="5" t="n">
@@ -12608,7 +12608,7 @@
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>Obesidad intensa</t>
+          <t>Obsesidad intesa</t>
         </is>
       </c>
       <c r="C34" s="5" t="n">
@@ -13038,7 +13038,7 @@
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>Obesidad intensa</t>
+          <t>Obsesidad intesa</t>
         </is>
       </c>
       <c r="C40" s="5" t="n">
